--- a/astro-site/public/dl/plan-negocio-polleria/checklist-apertura-polleria.xlsx
+++ b/astro-site/public/dl/plan-negocio-polleria/checklist-apertura-polleria.xlsx
@@ -3168,7 +3168,7 @@
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>Inspección periódica (red) o revisión (gas envasado) cada 5 años (RD 919/2006, ITC-ICG 08), y una revisión al año de los quemadores, el motor y las espadas del asador. Apunta las fechas</t>
+          <t>Inspección periódica (red) o revisión (gas envasado) cada 5 años (RD 919/2006, ITC-ICG 07), y una revisión al año de los quemadores, el motor y las espadas del asador. Apunta las fechas</t>
         </is>
       </c>
     </row>

--- a/astro-site/public/dl/plan-negocio-polleria/checklist-apertura-polleria.xlsx
+++ b/astro-site/public/dl/plan-negocio-polleria/checklist-apertura-polleria.xlsx
@@ -951,8 +951,8 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="A5 A6 A7 A8 A9 A10 A11 A12 A13 A14 A15 A16" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, —, N/A. N/A = no aplica, sale del total." type="list">
-      <formula1>"✓,—,N/A"</formula1>
+    <dataValidation sqref="A5 A6 A7 A8 A9 A10 A11 A12 A13 A14 A15 A16" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, ☐, N/A. N/A = no aplica, sale del total." type="list">
+      <formula1>"✓,☐,N/A"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
@@ -1463,8 +1463,8 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="A5 A6 A7 A8 A9 A10 A11 A12 A13 A14 A15 A16 A17 A18 A19" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, —, N/A. N/A = no aplica, sale del total." type="list">
-      <formula1>"✓,—,N/A"</formula1>
+    <dataValidation sqref="A5 A6 A7 A8 A9 A10 A11 A12 A13 A14 A15 A16 A17 A18 A19" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, ☐, N/A. N/A = no aplica, sale del total." type="list">
+      <formula1>"✓,☐,N/A"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
@@ -1952,8 +1952,8 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="A5 A6 A7 A8 A9 A10 A11 A12 A13 A14 A15 A16 A17 A18" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, —, N/A. N/A = no aplica, sale del total." type="list">
-      <formula1>"✓,—,N/A"</formula1>
+    <dataValidation sqref="A5 A6 A7 A8 A9 A10 A11 A12 A13 A14 A15 A16 A17 A18" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, ☐, N/A. N/A = no aplica, sale del total." type="list">
+      <formula1>"✓,☐,N/A"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
@@ -2413,8 +2413,8 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="A5 A6 A7 A8 A9 A10 A11 A12 A13 A14 A15 A16 A17" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, —, N/A. N/A = no aplica, sale del total." type="list">
-      <formula1>"✓,—,N/A"</formula1>
+    <dataValidation sqref="A5 A6 A7 A8 A9 A10 A11 A12 A13 A14 A15 A16 A17" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, ☐, N/A. N/A = no aplica, sale del total." type="list">
+      <formula1>"✓,☐,N/A"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
@@ -2881,8 +2881,8 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="A5 A6 A7 A8 A9 A10 A11 A12 A13 A14 A15 A16 A17" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, —, N/A. N/A = no aplica, sale del total." type="list">
-      <formula1>"✓,—,N/A"</formula1>
+    <dataValidation sqref="A5 A6 A7 A8 A9 A10 A11 A12 A13 A14 A15 A16 A17" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, ☐, N/A. N/A = no aplica, sale del total." type="list">
+      <formula1>"✓,☐,N/A"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
@@ -3339,8 +3339,8 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="A5 A6 A7 A8 A9 A10 A11 A12 A13 A14 A15 A16 A17" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, —, N/A. N/A = no aplica, sale del total." type="list">
-      <formula1>"✓,—,N/A"</formula1>
+    <dataValidation sqref="A5 A6 A7 A8 A9 A10 A11 A12 A13 A14 A15 A16 A17" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, ☐, N/A. N/A = no aplica, sale del total." type="list">
+      <formula1>"✓,☐,N/A"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
